--- a/Cari_Ex3A_tables.xlsx
+++ b/Cari_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vesnacari\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FE9DEA1-65C1-4A8F-BD64-E93A051BE08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F858093-4610-47C5-B11F-DC9E1B580157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="432" yWindow="504" windowWidth="15276" windowHeight="7764" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clients" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
   <si>
     <t>Clients</t>
   </si>
@@ -172,16 +172,114 @@
   </si>
   <si>
     <t>PaymentConfirmation</t>
+  </si>
+  <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClientID </t>
+  </si>
+  <si>
+    <t>ClientName</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>331-281-5664</t>
+  </si>
+  <si>
+    <t>Adam Jones</t>
+  </si>
+  <si>
+    <t>adamJones@gmail.com</t>
+  </si>
+  <si>
+    <t>221 Mulberry street</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DogID </t>
+  </si>
+  <si>
+    <t>Breed</t>
+  </si>
+  <si>
+    <t>ClientID</t>
+  </si>
+  <si>
+    <t>AppointmentID</t>
+  </si>
+  <si>
+    <t>DogID</t>
+  </si>
+  <si>
+    <t>D001</t>
+  </si>
+  <si>
+    <t>2026-40-20</t>
+  </si>
+  <si>
+    <t>D025</t>
+  </si>
+  <si>
+    <t>Buddy</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>C025</t>
+  </si>
+  <si>
+    <t>LogID</t>
+  </si>
+  <si>
+    <t>AppointentID</t>
+  </si>
+  <si>
+    <t>Good pace, calm behavior</t>
+  </si>
+  <si>
+    <t>PaymentID</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>CONF-AB123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -256,10 +354,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -275,8 +374,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -290,10 +403,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,15 +702,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="9.109375"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -609,7 +723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -617,69 +731,136 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>10</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="12">
+        <v>10010</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D13" r:id="rId1" xr:uid="{280C962E-60E6-4648-8FFE-26E777703519}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5947AA-205B-4511-AC34-23D5BBD39914}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>11</v>
       </c>
@@ -687,7 +868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -695,7 +876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -703,7 +884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -711,7 +892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
@@ -719,7 +900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
@@ -727,7 +908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -735,12 +916,52 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>1001</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F12" s="12">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -750,14 +971,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E7592D-DF2D-4A7E-8C8B-84B577A04CC5}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>23</v>
       </c>
@@ -765,7 +989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -773,7 +997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -781,7 +1005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -789,7 +1013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
@@ -797,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>28</v>
       </c>
@@ -805,12 +1029,46 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="17">
+        <v>43997</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -820,14 +1078,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203E78CF-12BB-479F-A3F5-DD1C1C27C4A7}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>31</v>
       </c>
@@ -835,7 +1097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -843,7 +1105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -851,7 +1113,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -859,7 +1121,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>34</v>
       </c>
@@ -867,7 +1129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>35</v>
       </c>
@@ -875,12 +1137,52 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>5001</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>1001</v>
+      </c>
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11">
+        <v>1.75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -890,14 +1192,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DD09CF6-F25D-44F7-B912-FE87F87D38EA}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
@@ -905,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -913,7 +1219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -921,7 +1227,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
@@ -929,7 +1235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>41</v>
       </c>
@@ -937,7 +1243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>42</v>
       </c>
@@ -945,12 +1251,52 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>9001</v>
+      </c>
+      <c r="B11" s="12">
+        <v>1001</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="12">
+        <v>35</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
